--- a/8035.T_report.xlsx
+++ b/8035.T_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,10 +449,30 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>手数料込み利益率(%)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>手数料(円)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>決済後資産(円)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>保有日数</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>決済理由</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>バックテスト結果</t>
         </is>
@@ -464,33 +484,47 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2022-01-11</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>45150</v>
+        <v>19415.66</v>
       </c>
       <c r="E2" t="n">
-        <v>47160</v>
+        <v>18703.25</v>
       </c>
       <c r="F2" t="n">
-        <v>4.45</v>
+        <v>-3.67</v>
       </c>
       <c r="G2" t="n">
-        <v>21</v>
-      </c>
-      <c r="I2" t="inlineStr">
+        <v>-3.87</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1963</v>
+      </c>
+      <c r="I2" t="n">
+        <v>961344</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>総取引回数</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>2</v>
+      <c r="M2" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -499,58 +533,379 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2023-03-10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2023-04-06</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55020</v>
+        <v>14856.26</v>
       </c>
       <c r="E3" t="n">
-        <v>69470</v>
+        <v>14202.44</v>
       </c>
       <c r="F3" t="n">
-        <v>26.26</v>
+        <v>-4.4</v>
       </c>
       <c r="G3" t="n">
-        <v>29</v>
-      </c>
-      <c r="I3" t="inlineStr">
+        <v>-4.6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1880</v>
+      </c>
+      <c r="I3" t="n">
+        <v>917155</v>
+      </c>
+      <c r="J3" t="n">
+        <v>27</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>勝率</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="I4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>20130.09</v>
+      </c>
+      <c r="E4" t="n">
+        <v>19910.75</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1824</v>
+      </c>
+      <c r="I4" t="n">
+        <v>905337</v>
+      </c>
+      <c r="J4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>atr_stop</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>総利益率</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>30.72%</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>38.20%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="I5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2024-01-04</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>24031.87</v>
+      </c>
+      <c r="E5" t="n">
+        <v>22796.77</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-5.14</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-5.33</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1764</v>
+      </c>
+      <c r="I5" t="n">
+        <v>857044</v>
+      </c>
+      <c r="J5" t="n">
+        <v>15</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>平均保有日数</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>25.0日</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>10.0日</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2024-01-12</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2024-01-19</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>24978.69</v>
+      </c>
+      <c r="E6" t="n">
+        <v>26809.12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="G6" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1777</v>
+      </c>
+      <c r="I6" t="n">
+        <v>918071</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>最終資産</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1382001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>23368.34</v>
+      </c>
+      <c r="E7" t="n">
+        <v>24860.1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1895</v>
+      </c>
+      <c r="I7" t="n">
+        <v>974783</v>
+      </c>
+      <c r="J7" t="n">
+        <v>12</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>手数料込み利益</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>382001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>45195.15</v>
+      </c>
+      <c r="E8" t="n">
+        <v>51668.28</v>
+      </c>
+      <c r="F8" t="n">
+        <v>14.32</v>
+      </c>
+      <c r="G8" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2089</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1112308</v>
+      </c>
+      <c r="J8" t="n">
+        <v>9</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>総手数料</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>18267</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>52472.42</v>
+      </c>
+      <c r="E9" t="n">
+        <v>60839.1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="G9" t="n">
+        <v>15.73</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2402</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1287263</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>69969.89999999999</v>
+      </c>
+      <c r="E10" t="n">
+        <v>75264.66</v>
+      </c>
+      <c r="F10" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="G10" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2672</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1382001</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>take_profit</t>
         </is>
       </c>
     </row>

--- a/8035.T_report.xlsx
+++ b/8035.T_report.xlsx
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20130.09</v>
+        <v>20130.1</v>
       </c>
       <c r="E4" t="n">
         <v>19910.75</v>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>24031.87</v>
+        <v>24031.88</v>
       </c>
       <c r="E5" t="n">
         <v>22796.77</v>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>24978.69</v>
+        <v>24978.68</v>
       </c>
       <c r="E6" t="n">
         <v>26809.12</v>
